--- a/test-data/gherkins.xlsx
+++ b/test-data/gherkins.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\indhu\Desktop\Indhuja Personal\QANinjas\test-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3194908E-8A50-43EC-A3F0-297A940E2053}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A60841E6-8BB5-4E3B-B7B5-3F737B32180E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{91EF47E3-D72F-4114-8B78-F2A927ADBA49}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="2" xr2:uid="{91EF47E3-D72F-4114-8B78-F2A927ADBA49}"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="1" r:id="rId1"/>
     <sheet name="Accounts" sheetId="2" r:id="rId2"/>
+    <sheet name="Calendar" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="45">
   <si>
     <t>Feature</t>
   </si>
@@ -76,9 +77,6 @@
     <t>user is in Create Account page</t>
   </si>
   <si>
-    <t>user enters all required information and hit on Save</t>
-  </si>
-  <si>
     <t>user should be redirected to the Account Overview page</t>
   </si>
   <si>
@@ -86,6 +84,93 @@
   </si>
   <si>
     <t>CRMAccounts</t>
+  </si>
+  <si>
+    <t>View Accounts</t>
+  </si>
+  <si>
+    <t>user is in View Accounts page</t>
+  </si>
+  <si>
+    <t>user searches and views the account</t>
+  </si>
+  <si>
+    <t>Sort Account Records</t>
+  </si>
+  <si>
+    <t>user sorts the account records</t>
+  </si>
+  <si>
+    <t>account records should be sorted successfully</t>
+  </si>
+  <si>
+    <t>Search Account using Global Search</t>
+  </si>
+  <si>
+    <t>user is in Home page</t>
+  </si>
+  <si>
+    <t>user searches the account using global search</t>
+  </si>
+  <si>
+    <t>user creates the account</t>
+  </si>
+  <si>
+    <t>Duplicate Account</t>
+  </si>
+  <si>
+    <t>user is in Accounts Overview page</t>
+  </si>
+  <si>
+    <t>user duplicates the account</t>
+  </si>
+  <si>
+    <t>duplicate account should be created successfully</t>
+  </si>
+  <si>
+    <t>Delete Account</t>
+  </si>
+  <si>
+    <t>user deletes the account</t>
+  </si>
+  <si>
+    <t>account should be deleted successfully</t>
+  </si>
+  <si>
+    <t>CRMCalendar</t>
+  </si>
+  <si>
+    <t>Schedule Meeting</t>
+  </si>
+  <si>
+    <t>user is in Schedule Meeting page</t>
+  </si>
+  <si>
+    <t>user inputs meeting details and saves meeting</t>
+  </si>
+  <si>
+    <t>user is in Meeting Overview page</t>
+  </si>
+  <si>
+    <t>Background</t>
+  </si>
+  <si>
+    <t>user successfully logged into the application</t>
+  </si>
+  <si>
+    <t>account should be created successfully</t>
+  </si>
+  <si>
+    <t>Schedule Call</t>
+  </si>
+  <si>
+    <t>user is in Schedule Call page</t>
+  </si>
+  <si>
+    <t>user inputs Call details and saves Call</t>
+  </si>
+  <si>
+    <t>user is in Calls Overview page</t>
   </si>
 </sst>
 </file>
@@ -460,7 +545,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
         <v>10</v>
@@ -474,7 +559,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
         <v>10</v>
@@ -488,7 +573,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
         <v>10</v>
@@ -507,7 +592,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60F1B922-B3E9-4333-8DFB-726EEAD00ADA}">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12.53125" customWidth="1"/>
@@ -531,44 +616,394 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
         <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
         <v>11</v>
       </c>
       <c r="C4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
         <v>9</v>
       </c>
+      <c r="D5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" t="s">
+        <v>4</v>
+      </c>
+      <c r="D12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" t="s">
+        <v>6</v>
+      </c>
+      <c r="D16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" t="s">
+        <v>4</v>
+      </c>
+      <c r="D18" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" t="s">
+        <v>6</v>
+      </c>
+      <c r="D19" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" t="s">
+        <v>32</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E98376BA-8865-4F7A-BE93-A95697A0E1C8}">
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="30.19921875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
